--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45904.79166666666</v>
+        <v>45904.83333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,135 +3199,6 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45904.83333333334</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK21"/>
+  <dimension ref="A1:AK22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45904.83333333334</v>
+        <v>45904.79166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,126 +3079,255 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Carolina Core</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>45904.83333333334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Tacoma Defiance</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Whitecaps II</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.83333333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,522 +2812,6 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45904.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Israel Liga Leumit</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Maccabi Herzliya</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Hapoel Nazareth Illit</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>45904.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>45904.79166666666</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Crown Legacy</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Carolina Core</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>45904.83333333334</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45904.79166666666</v>
+        <v>45904.83333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,135 +2683,6 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45904.83333333334</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.5</v>
       </c>
-      <c r="X2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="O2" t="n">
-        <v>4.56</v>
+        <v>4.12</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.84</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
         <v>2.4</v>
       </c>
-      <c r="T2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.32</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4.12</v>
+        <v>4.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,28 +669,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
         <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
         <v>3.5</v>
@@ -699,7 +699,7 @@
         <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.5</v>
@@ -708,7 +708,7 @@
         <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="Z2" t="n">
         <v>1.47</v>
@@ -807,13 +807,13 @@
         <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R3" t="n">
         <v>1.53</v>
@@ -831,10 +831,10 @@
         <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
         <v>2.4</v>
@@ -843,7 +843,7 @@
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AB3" t="n">
         <v>1.16</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="AH3" t="n">
         <v>1.24</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45904.83333333334</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,126 +2563,255 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Carolina Core</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45904.83333333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Tacoma Defiance</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Whitecaps II</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45904.83333333334</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,126 +2692,384 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Hapoel Kfar Saba</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bnei Yehuda</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>45904.54166666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Carolina Core</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>45904.83333333334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Tacoma Defiance</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Whitecaps II</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3.89</v>
+        <v>4.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V2" t="n">
         <v>1.1</v>
       </c>
       <c r="W2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.5</v>
       </c>
-      <c r="X2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.9</v>
       </c>
-      <c r="O3" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.01</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2.82</v>
+        <v>3.12</v>
       </c>
       <c r="R3" t="n">
         <v>1.53</v>
@@ -828,31 +828,31 @@
         <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Z3" t="n">
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AB3" t="n">
         <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.83333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,780 +2296,6 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MC Oran</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ES Mostaganem</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Israel Liga Leumit</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Hapoel Hadera</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Hapoel Acre</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>USM Khenchela</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Israel Liga Leumit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Hapoel Kfar Saba</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Bnei Yehuda</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Crown Legacy</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Carolina Core</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>45904.83333333334</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="13">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="O2" t="n">
-        <v>4.32</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
         <v>2.45</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
         <v>1.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AB2" t="n">
         <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,46 +798,46 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="O3" t="n">
-        <v>4.11</v>
+        <v>4.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="Z3" t="n">
         <v>1.5</v>
@@ -846,13 +846,13 @@
         <v>4.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45904.83333333334</v>
+        <v>45904.79166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,126 +2176,255 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Carolina Core</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45904.83333333334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Tacoma Defiance</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Whitecaps II</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="T2" t="n">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="U2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="V2" t="n">
         <v>1.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4.34</v>
+        <v>4.1</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="T3" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="U3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Z3" t="n">
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.5</v>
       </c>
     </row>
     <row r="6">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.5</v>
       </c>
     </row>
     <row r="7">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45904.79166666666</v>
+        <v>45904.83333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,135 +2296,6 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45904.83333333334</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M2" t="n">
         <v>3.05</v>
       </c>
-      <c r="M2" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="O2" t="n">
-        <v>4.34</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="T2" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="U2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
         <v>1.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X2" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Y2" t="n">
         <v>2.47</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Z3" t="n">
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AB3" t="n">
         <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
         <v>2.47</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AB2" t="n">
         <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="T3" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="U3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Z3" t="n">
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB3" t="n">
         <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="T2" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="U2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.47</v>
       </c>
       <c r="Z2" t="n">
         <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.8</v>
+        <v>4.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4.24</v>
+        <v>4.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Z3" t="n">
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AB3" t="n">
         <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.5</v>
       </c>
     </row>
     <row r="13">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45904.5</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>4.24</v>
+        <v>4.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="T2" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V2" t="n">
         <v>1.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Z2" t="n">
         <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="T3" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="U3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y3" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.47</v>
       </c>
       <c r="Z3" t="n">
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.8</v>
+        <v>4.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,55 +669,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>4.34</v>
+        <v>4.15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="U2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.47</v>
       </c>
       <c r="Z2" t="n">
         <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.8</v>
+        <v>5.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AC2" t="n">
         <v>2.12</v>
@@ -739,7 +739,7 @@
         <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4.24</v>
+        <v>4.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="R3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,55 +669,55 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>4.15</v>
+        <v>4.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.21</v>
+        <v>2.99</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T2" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="U2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.78</v>
+        <v>4.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
         <v>2.12</v>
@@ -739,7 +739,7 @@
         <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4.34</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
         <v>2.12</v>
@@ -868,7 +868,7 @@
         <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="O2" t="n">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W2" t="n">
         <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.8</v>
+        <v>5.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="M3" t="n">
         <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>4.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
         <v>2.34</v>
       </c>
       <c r="T3" t="n">
-        <v>3.66</v>
+        <v>3.48</v>
       </c>
       <c r="U3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.78</v>
+        <v>4.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -669,25 +669,25 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>4.28</v>
+        <v>4.15</v>
       </c>
       <c r="P2" t="n">
         <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
         <v>2.29</v>
@@ -702,22 +702,22 @@
         <v>1.12</v>
       </c>
       <c r="W2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.44</v>
       </c>
       <c r="AA2" t="n">
         <v>5.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" t="n">
         <v>2.19</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AH2" t="n">
         <v>1.32</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
         <v>2.94</v>
@@ -828,19 +828,19 @@
         <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
         <v>2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AA3" t="n">
         <v>4.6</v>
@@ -852,7 +852,7 @@
         <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.21</v>
+        <v>2.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="U2" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.78</v>
+        <v>4.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AA3" t="n">
-        <v>4.6</v>
+        <v>5.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,13 +684,13 @@
         <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="R2" t="n">
         <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="T2" t="n">
         <v>3.48</v>
@@ -816,19 +816,19 @@
         <v>3.21</v>
       </c>
       <c r="R3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="T3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="U3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
         <v>1.55</v>
@@ -843,16 +843,16 @@
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.78</v>
+        <v>5.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AC3" t="n">
         <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
         <v>1.32</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.83333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2167,135 +2167,6 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45904.83333333334</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45904.83333333334</v>
+        <v>45904.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,126 +2047,255 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Carolina Core</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>45904.83333333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Tacoma Defiance</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Whitecaps II</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>1.85</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>3.9</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N14" t="n">
         <v>3.2</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.78</v>
+        <v>3.21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.5</v>
       </c>
-      <c r="X2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AA2" t="n">
-        <v>4.6</v>
+        <v>5.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.21</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="T3" t="n">
-        <v>3.85</v>
+        <v>3.48</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.45</v>
+        <v>4.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
         <v>1.32</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.83333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1909,393 +1909,6 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CS Constantine</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>MB Rouisset</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Crown Legacy</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Carolina Core</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
-        <v>45904.83333333334</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="M2" t="n">
         <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="O2" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="T2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.78</v>
+        <v>4.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="O3" t="n">
         <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="V3" t="n">
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.6</v>
+        <v>5.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AH3" t="n">
         <v>1.32</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45904.54166666666</v>
+        <v>45904.83333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1264,651 +1264,6 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Paradou AC</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>El Bayadh</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>USM Khenchela</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3" t="n">
-        <v>45904.54166666666</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Crown Legacy</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Carolina Core</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>45904.83333333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="3" t="n">
         <v>45904.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,523 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45904.45833333334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Russia FNL</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Spartak Kostroma</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ural</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="3" t="n">
-        <v>45904.45833333334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Israel Liga Leumit</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Hapoel Ramat Gan</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Maccabi Petah Tikva</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="3" t="n">
         <v>45904.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Crown Legacy</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Carolina Core</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="3" t="n">
-        <v>45904.83333333334</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>45904.95833333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,127 +628,643 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Chelyabinsk</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fakel</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>45904.45833333334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Spartak Kostroma</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ural</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="3" t="n">
+        <v>45904.45833333334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Israel Liga Leumit</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hapoel Ramat Gan</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Maccabi Petah Tikva</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45904.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Crown Legacy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Carolina Core</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="3" t="n">
+        <v>45904.83333333334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Whitecaps II</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>45904.95833333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.5</v>
       </c>
-      <c r="X2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AA2" t="n">
-        <v>4.65</v>
+        <v>5.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.24</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="V3" t="n">
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.94</v>
+        <v>4.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="T2" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.94</v>
+        <v>4.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="V3" t="n">
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AA3" t="n">
-        <v>4.65</v>
+        <v>5.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
         <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1185,23 +1185,23 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="N6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3.25</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1209,37 +1209,37 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" t="n">
         <v>1.5</v>
       </c>
-      <c r="X2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AA2" t="n">
-        <v>4.65</v>
+        <v>5.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="V3" t="n">
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.94</v>
+        <v>4.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -678,28 +678,28 @@
         <v>1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="T2" t="n">
-        <v>3.88</v>
+        <v>4.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.55</v>
@@ -714,16 +714,16 @@
         <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.94</v>
+        <v>7.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -807,28 +807,28 @@
         <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>3.33</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
         <v>1.5</v>
@@ -843,16 +843,16 @@
         <v>1.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.65</v>
+        <v>5.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -652,20 +652,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -727,12 +727,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+10']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG3" t="n">

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,77 +669,77 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
       <c r="R2" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="T2" t="n">
-        <v>4.6</v>
+        <v>3.66</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1.1</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['90+10']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.55</v>
       </c>
-      <c r="O3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="AD3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['90+10']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['90+5']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="P5" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
         <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="X5" t="n">
         <v>4.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
         <v>2.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1188,58 +1188,58 @@
         <v>1.86</v>
       </c>
       <c r="M6" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
         <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,77 +669,77 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.55</v>
       </c>
-      <c r="O2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="AD2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
         <v>1.5</v>
       </c>
-      <c r="X2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>['90+10']</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>['90+5']</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
       <c r="R3" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="T3" t="n">
-        <v>4.6</v>
+        <v>3.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.1</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['90+10']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-09-04.xlsx
+++ b/jogos_2025-09-04.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,77 +669,77 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
       <c r="R2" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="T2" t="n">
-        <v>4.6</v>
+        <v>3.66</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1.1</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['90+10']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.55</v>
       </c>
-      <c r="O3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="AD3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['90+10']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['90+5']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1062,25 +1062,25 @@
         <v>3.54</v>
       </c>
       <c r="N5" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="O5" t="n">
         <v>2.71</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
         <v>1.57</v>
@@ -1104,7 +1104,7 @@
         <v>2.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC5" t="n">
         <v>1.44</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
         <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="U6" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
         <v>2.82</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
